--- a/viz/amin_data/manish_amin_modified_data/Total Opeation Cost.xlsx
+++ b/viz/amin_data/manish_amin_modified_data/Total Opeation Cost.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aminm\Box\Manish-Amin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AB057BC-DAEC-4336-A86D-4213C17A0BFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B72ED62-AFB8-4DAA-86CD-2B259D248A27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{7EF5785F-7EA7-4A4B-AEE3-87CE148439FC}"/>
   </bookViews>
@@ -131,19 +131,19 @@
     <t>WAUW</t>
   </si>
   <si>
-    <t>CASE 2</t>
-  </si>
-  <si>
-    <t>CASE 4</t>
-  </si>
-  <si>
-    <t>Case 3</t>
-  </si>
-  <si>
-    <t>case 1</t>
-  </si>
-  <si>
     <t>Total operaiton cost</t>
+  </si>
+  <si>
+    <t>case 0</t>
+  </si>
+  <si>
+    <t>CASE 1</t>
+  </si>
+  <si>
+    <t>Case 2</t>
+  </si>
+  <si>
+    <t>CASE 3</t>
   </si>
 </sst>
 </file>
@@ -192,10 +192,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -537,22 +539,23 @@
     <col min="3" max="3" width="10.26171875" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="12.26171875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="16.15625" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="11.68359375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.68359375" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="12.26171875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="8.9453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="3:18" x14ac:dyDescent="0.55000000000000004">
       <c r="O1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P1" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q1" t="s">
         <v>34</v>
       </c>
-      <c r="P1" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>33</v>
-      </c>
       <c r="R1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="3:18" x14ac:dyDescent="0.55000000000000004">
@@ -560,16 +563,16 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>8615019.1899999995</v>
+        <v>8577963.9700000007</v>
       </c>
       <c r="P2">
-        <v>8623956.9199999999</v>
+        <v>8628600.3599999994</v>
       </c>
       <c r="Q2">
-        <v>8604342.6300000008</v>
+        <v>8593854.7699999996</v>
       </c>
       <c r="R2">
-        <v>8599330.1799999997</v>
+        <v>8584408.5600000005</v>
       </c>
     </row>
     <row r="3" spans="3:18" x14ac:dyDescent="0.55000000000000004">
@@ -577,16 +580,16 @@
         <v>1</v>
       </c>
       <c r="O3">
-        <v>1117789.2</v>
+        <v>1251783.8600000001</v>
       </c>
       <c r="P3">
-        <v>1233766.0900000001</v>
+        <v>1118803.79</v>
       </c>
       <c r="Q3">
-        <v>1070233.4099999999</v>
+        <v>1074585.92</v>
       </c>
       <c r="R3">
-        <v>1064801.69</v>
+        <v>1060707.43</v>
       </c>
     </row>
     <row r="4" spans="3:18" x14ac:dyDescent="0.55000000000000004">
@@ -597,16 +600,16 @@
         <v>2</v>
       </c>
       <c r="O4" s="1">
-        <v>4445211.58</v>
+        <v>4568102.68</v>
       </c>
       <c r="P4">
-        <v>4483599.01</v>
+        <v>4514524.82</v>
       </c>
       <c r="Q4">
-        <v>4599325.84</v>
+        <v>4710083.9000000004</v>
       </c>
       <c r="R4">
-        <v>4243473.25</v>
+        <v>4346153.28</v>
       </c>
     </row>
     <row r="5" spans="3:18" x14ac:dyDescent="0.55000000000000004">
@@ -617,16 +620,16 @@
         <v>3</v>
       </c>
       <c r="O5" s="1">
-        <v>2232460.2799999998</v>
+        <v>2441445.7799999998</v>
       </c>
       <c r="P5">
-        <v>2747468.94</v>
+        <v>2222190.2400000002</v>
       </c>
       <c r="Q5">
-        <v>2149085.66</v>
+        <v>2069420.86</v>
       </c>
       <c r="R5">
-        <v>2037657.74</v>
+        <v>2021011.98</v>
       </c>
     </row>
     <row r="6" spans="3:18" x14ac:dyDescent="0.55000000000000004">
@@ -634,16 +637,16 @@
         <v>4</v>
       </c>
       <c r="O6">
-        <v>2543611.27</v>
+        <v>3010280.12</v>
       </c>
       <c r="P6">
-        <v>2868388.06</v>
+        <v>2556686.38</v>
       </c>
       <c r="Q6">
-        <v>2503665.52</v>
+        <v>2542118.4</v>
       </c>
       <c r="R6">
-        <v>2459143.27</v>
+        <v>2500812.5699999998</v>
       </c>
     </row>
     <row r="7" spans="3:18" x14ac:dyDescent="0.55000000000000004">
@@ -654,16 +657,16 @@
         <v>5</v>
       </c>
       <c r="O7" s="1">
-        <v>-1712071.63</v>
+        <v>-2305516.09</v>
       </c>
       <c r="P7">
-        <v>-2414477.62</v>
+        <v>-1839949.77</v>
       </c>
       <c r="Q7">
-        <v>-2125764.5499999998</v>
+        <v>-2151424.96</v>
       </c>
       <c r="R7">
-        <v>-2301658.7999999998</v>
+        <v>-2247116.69</v>
       </c>
     </row>
     <row r="8" spans="3:18" x14ac:dyDescent="0.55000000000000004">
@@ -671,16 +674,16 @@
         <v>6</v>
       </c>
       <c r="O8">
-        <v>1231951.55</v>
+        <v>1194108.3799999999</v>
       </c>
       <c r="P8">
-        <v>1224374.26</v>
+        <v>1229327.93</v>
       </c>
       <c r="Q8">
-        <v>1241392.57</v>
+        <v>1235501.08</v>
       </c>
       <c r="R8">
-        <v>1234306.83</v>
+        <v>1234325.52</v>
       </c>
     </row>
     <row r="9" spans="3:18" x14ac:dyDescent="0.55000000000000004">
@@ -688,16 +691,16 @@
         <v>7</v>
       </c>
       <c r="O9">
-        <v>-422011.17</v>
+        <v>-426130.51</v>
       </c>
       <c r="P9">
-        <v>-445922.21</v>
+        <v>-439895.91</v>
       </c>
       <c r="Q9">
-        <v>-439560.58</v>
+        <v>-415669.45</v>
       </c>
       <c r="R9">
-        <v>-421915.3</v>
+        <v>-417357.45</v>
       </c>
     </row>
     <row r="10" spans="3:18" x14ac:dyDescent="0.55000000000000004">
@@ -708,16 +711,16 @@
         <v>8</v>
       </c>
       <c r="O10" s="1">
-        <v>14591489.609999999</v>
+        <v>15819951.77</v>
       </c>
       <c r="P10">
-        <v>14811760.49</v>
+        <v>14490521.060000001</v>
       </c>
       <c r="Q10">
-        <v>15121745.699999999</v>
+        <v>14251480.779999999</v>
       </c>
       <c r="R10">
-        <v>14234542.09</v>
+        <v>14195328.609999999</v>
       </c>
     </row>
     <row r="11" spans="3:18" x14ac:dyDescent="0.55000000000000004">
@@ -725,16 +728,16 @@
         <v>9</v>
       </c>
       <c r="O11">
-        <v>-211828.31</v>
+        <v>-230272.03</v>
       </c>
       <c r="P11">
-        <v>-244300.14</v>
+        <v>-221806.85</v>
       </c>
       <c r="Q11">
-        <v>-215487.59</v>
+        <v>-208829.09</v>
       </c>
       <c r="R11">
-        <v>-211063.91</v>
+        <v>-208681.36</v>
       </c>
     </row>
     <row r="12" spans="3:18" x14ac:dyDescent="0.55000000000000004">
@@ -742,16 +745,16 @@
         <v>10</v>
       </c>
       <c r="O12">
-        <v>1212651.55</v>
+        <v>1268773.6000000001</v>
       </c>
       <c r="P12">
-        <v>1225975.81</v>
+        <v>1242982.96</v>
       </c>
       <c r="Q12">
-        <v>1282432.47</v>
+        <v>1246741.07</v>
       </c>
       <c r="R12">
-        <v>1231900.78</v>
+        <v>1227118.8999999999</v>
       </c>
     </row>
     <row r="13" spans="3:18" x14ac:dyDescent="0.55000000000000004">
@@ -759,16 +762,16 @@
         <v>11</v>
       </c>
       <c r="O13">
-        <v>-173338.06</v>
+        <v>-173890.26</v>
       </c>
       <c r="P13">
-        <v>-187817.06</v>
+        <v>-183510.96</v>
       </c>
       <c r="Q13">
-        <v>-183281.99</v>
+        <v>-176279.79</v>
       </c>
       <c r="R13">
-        <v>-179994.28</v>
+        <v>-178072.06</v>
       </c>
     </row>
     <row r="14" spans="3:18" x14ac:dyDescent="0.55000000000000004">
@@ -776,16 +779,16 @@
         <v>12</v>
       </c>
       <c r="O14">
-        <v>-102627.32</v>
+        <v>-113460.54</v>
       </c>
       <c r="P14">
-        <v>-107807.29</v>
+        <v>-107745.98</v>
       </c>
       <c r="Q14">
-        <v>-117171.77</v>
+        <v>-107322.84</v>
       </c>
       <c r="R14">
-        <v>-110234.26</v>
+        <v>-110472.74</v>
       </c>
     </row>
     <row r="15" spans="3:18" x14ac:dyDescent="0.55000000000000004">
@@ -796,16 +799,16 @@
         <v>13</v>
       </c>
       <c r="O15" s="1">
-        <v>913131.43</v>
+        <v>912822.45</v>
       </c>
       <c r="P15">
-        <v>898171.4</v>
+        <v>927443.85</v>
       </c>
       <c r="Q15">
-        <v>910651.29</v>
+        <v>898726.34</v>
       </c>
       <c r="R15">
-        <v>876607.92</v>
+        <v>875136.96</v>
       </c>
     </row>
     <row r="16" spans="3:18" x14ac:dyDescent="0.55000000000000004">
@@ -816,16 +819,16 @@
         <v>14</v>
       </c>
       <c r="O16" s="1">
-        <v>2498899.7000000002</v>
+        <v>2541568.4300000002</v>
       </c>
       <c r="P16">
-        <v>2524333.5499999998</v>
+        <v>2534082.52</v>
       </c>
       <c r="Q16">
-        <v>2583115.83</v>
+        <v>2588158.4300000002</v>
       </c>
       <c r="R16">
-        <v>2525311.58</v>
+        <v>2534515.36</v>
       </c>
     </row>
     <row r="17" spans="3:18" x14ac:dyDescent="0.55000000000000004">
@@ -836,16 +839,16 @@
         <v>15</v>
       </c>
       <c r="O17" s="1">
-        <v>3036264.48</v>
+        <v>2887195.68</v>
       </c>
       <c r="P17">
-        <v>2871951.21</v>
+        <v>2876619.05</v>
       </c>
       <c r="Q17">
-        <v>3077959.47</v>
+        <v>2954258.91</v>
       </c>
       <c r="R17">
-        <v>3167602.76</v>
+        <v>3327543.28</v>
       </c>
     </row>
     <row r="18" spans="3:18" x14ac:dyDescent="0.55000000000000004">
@@ -856,16 +859,16 @@
         <v>16</v>
       </c>
       <c r="O18" s="2">
-        <v>-573078.99</v>
+        <v>-854550.29</v>
       </c>
       <c r="P18">
-        <v>-802471.62</v>
+        <v>-583106.84</v>
       </c>
       <c r="Q18">
-        <v>-482128.66</v>
+        <v>-480110.99</v>
       </c>
       <c r="R18">
-        <v>-468541.84</v>
+        <v>-458287.19</v>
       </c>
     </row>
     <row r="19" spans="3:18" x14ac:dyDescent="0.55000000000000004">
@@ -876,16 +879,16 @@
         <v>17</v>
       </c>
       <c r="O19" s="1">
-        <v>1680591.56</v>
+        <v>1541005.54</v>
       </c>
       <c r="P19">
-        <v>1538888.86</v>
+        <v>1527223.31</v>
       </c>
       <c r="Q19">
-        <v>1530672.17</v>
+        <v>1633355.65</v>
       </c>
       <c r="R19">
-        <v>1632860.79</v>
+        <v>1584179.93</v>
       </c>
     </row>
     <row r="20" spans="3:18" x14ac:dyDescent="0.55000000000000004">
@@ -896,16 +899,16 @@
         <v>18</v>
       </c>
       <c r="O20" s="1">
-        <v>2160031.0299999998</v>
+        <v>2384163.7200000002</v>
       </c>
       <c r="P20">
-        <v>2327876.0499999998</v>
+        <v>2162058.9</v>
       </c>
       <c r="Q20">
-        <v>1927879.82</v>
+        <v>1886275.99</v>
       </c>
       <c r="R20">
-        <v>1791934.95</v>
+        <v>1792187.32</v>
       </c>
     </row>
     <row r="21" spans="3:18" x14ac:dyDescent="0.55000000000000004">
@@ -913,16 +916,16 @@
         <v>19</v>
       </c>
       <c r="O21">
-        <v>2730894.12</v>
+        <v>3097792.23</v>
       </c>
       <c r="P21">
-        <v>3053400.91</v>
+        <v>2756567.7</v>
       </c>
       <c r="Q21">
-        <v>2621117.62</v>
+        <v>2611591.14</v>
       </c>
       <c r="R21">
-        <v>2590588.7999999998</v>
+        <v>2571376.0699999998</v>
       </c>
     </row>
     <row r="22" spans="3:18" x14ac:dyDescent="0.55000000000000004">
@@ -933,16 +936,16 @@
         <v>20</v>
       </c>
       <c r="O22" s="1">
-        <v>853513.84</v>
+        <v>844095.8</v>
       </c>
       <c r="P22">
-        <v>844619.82</v>
+        <v>837255.37</v>
       </c>
       <c r="Q22">
-        <v>852727.75</v>
+        <v>870561.89</v>
       </c>
       <c r="R22">
-        <v>846878.38</v>
+        <v>856204.92</v>
       </c>
     </row>
     <row r="23" spans="3:18" x14ac:dyDescent="0.55000000000000004">
@@ -953,16 +956,16 @@
         <v>21</v>
       </c>
       <c r="O23" s="1">
-        <v>1762934.28</v>
+        <v>1763445.17</v>
       </c>
       <c r="P23">
-        <v>1746347.37</v>
+        <v>1729161.81</v>
       </c>
       <c r="Q23">
-        <v>1804506</v>
+        <v>1805721.28</v>
       </c>
       <c r="R23">
-        <v>1816167.41</v>
+        <v>1814010.82</v>
       </c>
     </row>
     <row r="24" spans="3:18" x14ac:dyDescent="0.55000000000000004">
@@ -970,16 +973,16 @@
         <v>22</v>
       </c>
       <c r="O24">
-        <v>3222194.18</v>
+        <v>3666726.35</v>
       </c>
       <c r="P24">
-        <v>3615853.35</v>
+        <v>3248305.16</v>
       </c>
       <c r="Q24">
-        <v>3055302.57</v>
+        <v>3048017.71</v>
       </c>
       <c r="R24">
-        <v>3015659.16</v>
+        <v>2991468.13</v>
       </c>
     </row>
     <row r="25" spans="3:18" x14ac:dyDescent="0.55000000000000004">
@@ -987,16 +990,16 @@
         <v>23</v>
       </c>
       <c r="O25">
-        <v>924950.44</v>
+        <v>1231554</v>
       </c>
       <c r="P25">
-        <v>1106194.29</v>
+        <v>928194.21</v>
       </c>
       <c r="Q25">
-        <v>830176.19</v>
+        <v>839900.1</v>
       </c>
       <c r="R25">
-        <v>817827.43</v>
+        <v>809674.02</v>
       </c>
     </row>
     <row r="26" spans="3:18" x14ac:dyDescent="0.55000000000000004">
@@ -1007,16 +1010,16 @@
         <v>24</v>
       </c>
       <c r="O26" s="1">
-        <v>278046.89</v>
+        <v>168004.87</v>
       </c>
       <c r="P26">
-        <v>230919.82</v>
+        <v>195509.58</v>
       </c>
       <c r="Q26">
-        <v>229002.03</v>
+        <v>367697.99</v>
       </c>
       <c r="R26">
-        <v>205059.12</v>
+        <v>-486.17</v>
       </c>
     </row>
     <row r="27" spans="3:18" x14ac:dyDescent="0.55000000000000004">
@@ -1024,16 +1027,16 @@
         <v>25</v>
       </c>
       <c r="O27">
-        <v>1708415.53</v>
+        <v>1736506.13</v>
       </c>
       <c r="P27">
-        <v>1712723.66</v>
+        <v>1721699.44</v>
       </c>
       <c r="Q27">
-        <v>1745170.07</v>
+        <v>1726271.44</v>
       </c>
       <c r="R27">
-        <v>1715858.76</v>
+        <v>1713371.05</v>
       </c>
     </row>
     <row r="28" spans="3:18" x14ac:dyDescent="0.55000000000000004">
@@ -1058,16 +1061,16 @@
         <v>27</v>
       </c>
       <c r="O29">
-        <v>429596.53</v>
+        <v>493476.68</v>
       </c>
       <c r="P29">
-        <v>502838.37</v>
+        <v>433285.47</v>
       </c>
       <c r="Q29">
-        <v>403392.36</v>
+        <v>399650.94</v>
       </c>
       <c r="R29">
-        <v>398473.53</v>
+        <v>394977</v>
       </c>
     </row>
     <row r="30" spans="3:18" x14ac:dyDescent="0.55000000000000004">
@@ -1075,16 +1078,16 @@
         <v>28</v>
       </c>
       <c r="O30">
-        <v>854194.56</v>
+        <v>799010.84</v>
       </c>
       <c r="P30">
-        <v>813177.57</v>
+        <v>805395.91</v>
       </c>
       <c r="Q30">
-        <v>760615.06</v>
+        <v>800031.42</v>
       </c>
       <c r="R30">
-        <v>815970.25</v>
+        <v>820046.54</v>
       </c>
     </row>
     <row r="31" spans="3:18" x14ac:dyDescent="0.55000000000000004">
@@ -1092,16 +1095,16 @@
         <v>29</v>
       </c>
       <c r="O31">
-        <v>-148608.54</v>
+        <v>-240218.93</v>
       </c>
       <c r="P31">
-        <v>-171537.01</v>
+        <v>-197294.84</v>
       </c>
       <c r="Q31">
-        <v>-245715.43</v>
+        <v>-191997.92</v>
       </c>
       <c r="R31">
-        <v>-176513.09</v>
+        <v>-169120.29</v>
       </c>
     </row>
     <row r="32" spans="3:18" x14ac:dyDescent="0.55000000000000004">
@@ -1109,33 +1112,33 @@
         <v>30</v>
       </c>
       <c r="O32">
-        <v>137668.6</v>
+        <v>172920.19</v>
       </c>
       <c r="P32">
-        <v>164619.75</v>
+        <v>138870.5</v>
       </c>
       <c r="Q32">
-        <v>126619.14</v>
+        <v>126345.44</v>
       </c>
       <c r="R32">
-        <v>124367.81</v>
+        <v>123001.13</v>
       </c>
     </row>
     <row r="33" spans="14:18" x14ac:dyDescent="0.55000000000000004">
       <c r="N33" t="s">
-        <v>35</v>
-      </c>
-      <c r="O33">
-        <v>52810590.390000015</v>
-      </c>
-      <c r="P33">
-        <v>52530532.480000012</v>
-      </c>
-      <c r="Q33">
-        <v>52107243.75</v>
+        <v>31</v>
+      </c>
+      <c r="O33" s="3">
+        <v>52544966.600000001</v>
+      </c>
+      <c r="P33" s="4">
+        <v>52374002.399999999</v>
+      </c>
+      <c r="Q33" s="4">
+        <v>52076601.579999998</v>
       </c>
       <c r="R33">
-        <v>50928364.450000018</v>
+        <v>50928022.560000002</v>
       </c>
     </row>
   </sheetData>
